--- a/reports/연금저축_이벤트_시뮬레이션_보고서.xlsx
+++ b/reports/연금저축_이벤트_시뮬레이션_보고서.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="요약" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="가정및방법론" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Nowcast_5_7월" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="향후회차예측" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="참고실적" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="방법론_상세" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Nowcast_5_7월" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="향후회차예측" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="참고실적" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
     <numFmt numFmtId="171" formatCode="0.000&quot;x&quot;"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +75,23 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
@@ -132,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,6 +235,18 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1104,6 +1134,380 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="118" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>예상치 산출 원리 · 방법론 · 계산 과정 (상세)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>0. 큰 그림 — 추정의 원리</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>이벤트 예산은 결국 '몇 명에게 얼마를 주느냐'로 결정된다. 문제는 '몇 명이 신청할지'를 좌우하는 상위 퍼널(광고 노출 → 페이지 도달 → 참여 클릭)이 내부에서 관측되지 않는다는 점이다(노출수·도달수·단계별 전환율 데이터 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>그래서 이 미관측 구간을 억지로 추정하지 않고, 관측 가능한 지표로 '신청자 수'를 직접 추정(reduced-form)한 뒤, 그 아래 단계(신청→순입금→조건충족→지급)만 실측 비율로 전개한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>추정 대상이 두 종류라 방법이 다르다:  (A) 진행 중 이벤트(5~7월) = 부분 실적 있음 → Nowcast(진행 추세 외삽).  (B) 미래 이벤트(26.8월~) = 실적 없음 → take-rate 모델 예측.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>1. 신청자 수 예측 — 미래 회차 (take-rate 2단계 모델)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>미래 회차는 신청자 수는 물론 '기준 고객수'조차 비어 있어 2단계로 추정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>[왜 take-rate인가] 신청자 절대 규모는 연금저축 가입 고객 기반이 커질수록 늘어난다. 그래서 신청자를 그대로 예측하지 않고 신청자 ÷ 기준 고객수 = take-rate(신청률)로 정규화한다. 고객 기반 성장 효과를 제거해 회차 간 비교가 가능한 안정적 비율이 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>[Stage 1 — 기준 고객수 투영] 연금저축 종료연월 고객수의 회차별 성장률을 계산해 미래로 연장한다. 성장에 계절성이 있어(연말정산 시기 유입↑) 도착 시즌별 평균 성장률을 쓴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>마지막 실적 2026_02 = 1,836,227명.  시즌 성장률 _03×1.0396 / _04×1.0746 / _01×1.0559</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>2026_03 = 1,836,227 × 1.0396 = 1,909,026명</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>2026_04 = 1,909,026 × 1.0746 = 2,051,354명</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>2027_01 = 2,051,354 × 1.0559 = 2,166,016명</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>[Stage 2 — 시즌 take-rate 적용] take-rate = (해당 시즌 과거 평균)과 (최근 4회차 평균)의 50:50 블렌드. 시즌 평균으로 계절성을, 최근 평균으로 프로그램 성숙(상승 추세)을 함께 반영한다. 초기 파일럿 회차(2024_03)는 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>예) 2026_03(_03 시즌): 시즌평균 0.94% 와 최근추세 1.25% 의 블렌드 = 1.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>신청자(기준) = 1,909,026 × 1.10% ≈ 20,930명</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>[시나리오 밴드] 기준 take-rate에 ±CV(변동계수) 적용 → 보수/낙관. CV는 그 시즌 과거 관측의 변동성(최소 0.15, 관측 1개뿐이면 0.25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>2026_03: 보수 0.82% / 기준 1.10% / 낙관 1.37% → 신청 15,698 / 20,930 / 26,163명</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>2026_04·2027_01도 동일 절차. (기준 신청 각 26,132 / 26,786명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>2. 신청자 수 예측 — 진행 중 5~7월 (Nowcast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>5~7월은 진행 중(잔여 7일)이라 '예측'이 아니라 관측된 진행 추세를 최종치로 외삽한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>총기간 92일(5/1~7/31 가정), 잔여 7일 → 경과 85일</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>현재 누적 신청 16,356명 → 일평균 = 16,356 ÷ 85 = 192.4명/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>잔여 7일 추가 유입 = 192.4 × 7 × 계수  (보수 0.5 / 기준 1.0 / 낙관 1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  기준: 192.4×7×1.0 = 1,347명 → 최종 신청 = 16,356 + 1,347 = 17,703명</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  보수: +673 → 17,029명   /   낙관: +2,020 → 18,376명</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>uplift(확장배수) = 최종신청 ÷ 현재신청.  기준 = 17,703 ÷ 16,356 = 1.082</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>순입금·당첨은 신청과 같은 비율로 늘어난다고 보고(퍼널 비율 일정 가정) uplift를 곱한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>최종 순입금(기준) = 10,459 × 1.082 = 11,320명</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>최종 당첨(기준)   = 5,315 × 1.082 = 5,753명</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>[계수의 의미] 보수=잔여기간 유입이 지금까지 일평균의 절반으로 둔화. 기준=현재 속도 유지(선형). 낙관=마감 임박 유입 가속(1.5배).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>3. 예산 산출 — 지급 퍼널 (조건충족 전원지급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>연금저축 이벤트는 추첨이 아니라 조건 충족 시 전원 지급. 지급 인원은 신청자 전체가 아니라 아래 2단계를 통과한 '당첨(조건충족)고객'이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>신청 →(전환율=순입금/신청)→ 순입금 →(조건충족률=당첨/순입금)→ 당첨 → 전원지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>오늘자 5~7월 실측: 전환율 10,459/16,356 = 63.9%,  조건충족 5,315/10,459 = 50.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>→ 지급률(당첨/신청) = 5,315/16,356 = 32.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t>리워드 단가 = 예산 ÷ 당첨 = 678,543,590 ÷ 5,315 = 127,665원 (=12.7665만원, 제세 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>[예산 공식] 예산 = 당첨(조건충족)고객 × 리워드 단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>5~7월 최종(기준): 5,753 × 127,665 = 7.34억</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>향후 2026_03 기준: 당첨 = 20,930 × 32.5% = 6,802명 → × 127,665 = 8.68억</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>[흔한 오류·정정] 지급률에 '전환율(62%)'을 그대로 쓰면 안 된다. 리워드는 순입금고객 전원이 아니라 그중 조건 충족한 44%(당첨)에게만 간다. 전환율로 계산하면 순입금/당첨 = 2.26배 과대. 반드시 전환율×조건충족률 두 단계를 곱해야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>4. 가정 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>· 5~7월 총기간 92일(5/1~7/31). 실제 기간이 다르면 일평균·잔여유입 재계산 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>· 잔여유입 계수 0.5/1.0/1.5 = 잔여기간 유입 패턴 가정(마감 급증 여부).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t>· 순입금·당첨이 신청과 동일 비율로 확장(퍼널 비율 일정) 가정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="33" t="inlineStr">
+        <is>
+          <t>· 향후 회차 지급률 32.5%(최근 실측). 10회차 평균 27.6% 적용 시 예산 ×0.85.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>· 리워드 12.7665만원은 제세 포함 → 세금 미가산.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>5. 한계</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>· 향후 회차 신청 예측은 take-rate 모델(고객기반) 산출로, 실제 이벤트 신청규모(분기 14~20천명)보다 높게 나오는 경향 → 상한 성격. 실적 추세로 하향 보정 여지 있음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="33" t="inlineStr">
+        <is>
+          <t>· 미래 이벤트는 실적이 없어 포인트 예측 검증 불가(26.8~10월 종료 후 첫 검증).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="33" t="inlineStr">
+        <is>
+          <t>· 표본이 작아(시즌당 1~2개) take-rate 시즌평균의 불확실성 존재.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1274,7 +1678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1495,7 +1899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/reports/연금저축_이벤트_시뮬레이션_보고서.xlsx
+++ b/reports/연금저축_이벤트_시뮬레이션_보고서.xlsx
@@ -12,7 +12,8 @@
     <sheet name="방법론_상세" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Nowcast_5_7월" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="향후회차예측" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="참고실적" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="몬테카를로" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="참고실적" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="#,##0&quot;명&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000&quot;억&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot;원&quot;"/>
@@ -31,6 +32,7 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="0.000&quot;x&quot;"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="173" formatCode="0.00&quot;억&quot;"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -96,7 +98,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +123,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -150,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,6 +255,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1905,6 +1922,239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>몬테카를로 예산 분포 (불확실성 정량화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>방법: 40,000회 시뮬레이션. 신청자 = 기준고객수 × take-rate(삼각분포: 보수/기준/낙관),</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      지급률 = Beta(평균 32.5%, 실적 변동계수 CV 0.22), 리워드 12.7665만원 고정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>각 시행마다 예산을 계산해 분포를 얻고, P90(90퍼센타일)을 예산 편성 권고치로 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>결정론 3점 시나리오(보수/기준/낙관)와 달리, 변수들의 확률분포를 결합해 상방 리스크를 정량화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>회차</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>기대값</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>P50(중앙)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>P90(편성 권고)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026_03</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>8.687439130319127</v>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>8.539455828580657</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>11.53164664064756</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>12.46410484713017</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026_04</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>10.85976506726833</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>10.7238360608835</v>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>14.23489613344813</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>15.30976328263765</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2027_01</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>11.13250183497256</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>10.99394573515692</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>14.55346538324864</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>15.65118782723832</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>3회차 합(포트폴리오)</t>
+        </is>
+      </c>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="36" t="n">
+        <v>30.53173521123299</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>36.22293172573622</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>37.83728429150365</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   └ 참고: 각 회차 P90 단순합 = 40.3억 (분산효과 무시로 과대. 포트폴리오 P90 36.2억이 정확).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>[ 진행 중 5~7월 최종(잔여유입 삼각분포) ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>기대값</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>5~7월 최종</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="n">
+        <v>7.345139337193686</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>7.344914818968542</v>
+      </c>
+      <c r="D16" s="37" t="n">
+        <v>7.500374552453503</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>7.536014135304152</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>※ 5~7월은 잔여 7일뿐이라 분포가 좁음(거의 확정). 향후 회차는 take-rate·지급률 불확실성으로 P90이 기준 대비 큼.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
